--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K391"/>
+  <dimension ref="A1:K392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15693,6 +15693,45 @@
         <v>500.2</v>
       </c>
       <c r="K391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>465.53</v>
+      </c>
+      <c r="C392" t="n">
+        <v>457.22</v>
+      </c>
+      <c r="D392" t="n">
+        <v>463.71</v>
+      </c>
+      <c r="E392" t="n">
+        <v>468.54</v>
+      </c>
+      <c r="F392" t="n">
+        <v>468.04</v>
+      </c>
+      <c r="G392" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="H392" t="n">
+        <v>484.02</v>
+      </c>
+      <c r="I392" t="n">
+        <v>494.26</v>
+      </c>
+      <c r="J392" t="n">
+        <v>500.89</v>
+      </c>
+      <c r="K392" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15709,7 +15748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19702,6 +19741,16 @@
       </c>
       <c r="B399" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -19870,28 +19919,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.304998024300079</v>
+        <v>6.303405271337102</v>
       </c>
       <c r="J2" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K2" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5445961834539335</v>
+        <v>0.5459085812064759</v>
       </c>
       <c r="M2" t="n">
-        <v>32.83581866030421</v>
+        <v>32.7634090876084</v>
       </c>
       <c r="N2" t="n">
-        <v>1899.05287552534</v>
+        <v>1894.22090926298</v>
       </c>
       <c r="O2" t="n">
-        <v>43.57812381832586</v>
+        <v>43.52264823356892</v>
       </c>
       <c r="P2" t="n">
-        <v>301.978546432586</v>
+        <v>301.9945057088601</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19948,28 +19997,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.21155227496004</v>
+        <v>6.208300005159076</v>
       </c>
       <c r="J3" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K3" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L3" t="n">
-        <v>0.654510518477373</v>
+        <v>0.6555667489460679</v>
       </c>
       <c r="M3" t="n">
-        <v>28.54794819185782</v>
+        <v>28.4976304000773</v>
       </c>
       <c r="N3" t="n">
-        <v>1163.492433396218</v>
+        <v>1160.620761858459</v>
       </c>
       <c r="O3" t="n">
-        <v>34.11000488707409</v>
+        <v>34.06788461085394</v>
       </c>
       <c r="P3" t="n">
-        <v>299.4111015041628</v>
+        <v>299.4436890261941</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20026,28 +20075,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.292262458082706</v>
+        <v>6.289849979937255</v>
       </c>
       <c r="J4" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K4" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6553634140252232</v>
+        <v>0.6564909945286503</v>
       </c>
       <c r="M4" t="n">
-        <v>28.95990379029895</v>
+        <v>28.90303534749686</v>
       </c>
       <c r="N4" t="n">
-        <v>1189.427348220748</v>
+        <v>1186.442566540307</v>
       </c>
       <c r="O4" t="n">
-        <v>34.48807544964996</v>
+        <v>34.44477560589279</v>
       </c>
       <c r="P4" t="n">
-        <v>302.1093336997513</v>
+        <v>302.1335065665571</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20104,28 +20153,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.503564477261794</v>
+        <v>6.503289971686864</v>
       </c>
       <c r="J5" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K5" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6614410429813766</v>
+        <v>0.6627222063962803</v>
       </c>
       <c r="M5" t="n">
-        <v>29.70577189678236</v>
+        <v>29.631879455718</v>
       </c>
       <c r="N5" t="n">
-        <v>1236.776269776125</v>
+        <v>1233.613900105356</v>
       </c>
       <c r="O5" t="n">
-        <v>35.16783004076488</v>
+        <v>35.12284014861777</v>
       </c>
       <c r="P5" t="n">
-        <v>297.1467114220108</v>
+        <v>297.1494619491867</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20182,28 +20231,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.298721310209129</v>
+        <v>6.298417758714357</v>
       </c>
       <c r="J6" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K6" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L6" t="n">
-        <v>0.678291905462188</v>
+        <v>0.6795375368600685</v>
       </c>
       <c r="M6" t="n">
-        <v>27.59201453062795</v>
+        <v>27.52373564744371</v>
       </c>
       <c r="N6" t="n">
-        <v>1074.967205809188</v>
+        <v>1072.218835169557</v>
       </c>
       <c r="O6" t="n">
-        <v>32.78669251097444</v>
+        <v>32.74475278834087</v>
       </c>
       <c r="P6" t="n">
-        <v>302.1181686636773</v>
+        <v>302.1212102289929</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20260,28 +20309,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.317152587963297</v>
+        <v>6.315406408079648</v>
       </c>
       <c r="J7" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K7" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6716812347250938</v>
+        <v>0.6728338824577458</v>
       </c>
       <c r="M7" t="n">
-        <v>27.8356433630289</v>
+        <v>27.77744769437847</v>
       </c>
       <c r="N7" t="n">
-        <v>1114.346619427209</v>
+        <v>1111.526612109311</v>
       </c>
       <c r="O7" t="n">
-        <v>33.38183067818792</v>
+        <v>33.3395652657516</v>
       </c>
       <c r="P7" t="n">
-        <v>300.9315515063461</v>
+        <v>300.9490481099218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20338,28 +20387,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.135111630539823</v>
+        <v>7.134848373223862</v>
       </c>
       <c r="J8" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K8" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L8" t="n">
-        <v>0.674572499228983</v>
+        <v>0.6758306775892575</v>
       </c>
       <c r="M8" t="n">
-        <v>31.89703307429682</v>
+        <v>31.81747071973056</v>
       </c>
       <c r="N8" t="n">
-        <v>1403.047060008378</v>
+        <v>1399.459385867433</v>
       </c>
       <c r="O8" t="n">
-        <v>37.45726978849871</v>
+        <v>37.4093489099641</v>
       </c>
       <c r="P8" t="n">
-        <v>295.9129926473939</v>
+        <v>295.9156304677806</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20416,28 +20465,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.681017840413213</v>
+        <v>7.679830306943333</v>
       </c>
       <c r="J9" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K9" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6773989894134915</v>
+        <v>0.678598314265618</v>
       </c>
       <c r="M9" t="n">
-        <v>34.25539206775238</v>
+        <v>34.17677574041283</v>
       </c>
       <c r="N9" t="n">
-        <v>1605.106308717153</v>
+        <v>1601.015045173995</v>
       </c>
       <c r="O9" t="n">
-        <v>40.06377801352679</v>
+        <v>40.01268605297569</v>
       </c>
       <c r="P9" t="n">
-        <v>293.5365663747704</v>
+        <v>293.5484653793059</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20494,28 +20543,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.712095911693027</v>
+        <v>7.711888387211888</v>
       </c>
       <c r="J10" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K10" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6822426695428578</v>
+        <v>0.6834894759513621</v>
       </c>
       <c r="M10" t="n">
-        <v>33.96831904855711</v>
+        <v>33.88301227265173</v>
       </c>
       <c r="N10" t="n">
-        <v>1582.510569037858</v>
+        <v>1578.463650926519</v>
       </c>
       <c r="O10" t="n">
-        <v>39.78078140305765</v>
+        <v>39.72988360071697</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4141419504778</v>
+        <v>297.4162213316531</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20553,7 +20602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K391"/>
+  <dimension ref="A1:K392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42843,6 +42892,63 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-42.21787783147837,173.8643998167743</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-42.21795380207272,173.86350103520076</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-42.218125012486205,173.8627963298359</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-42.21839790467025,173.86218808463525</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-42.21866894160701,173.8614822281533</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-42.2189842507633,173.86077721744894</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-42.21949511831076,173.86017970887687</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-42.21990271145572,173.85960680052852</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-42.220335952135706,173.85906702748989</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K392"/>
+  <dimension ref="A1:K394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15734,6 +15734,84 @@
       <c r="K392" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>466.28</v>
+      </c>
+      <c r="C393" t="n">
+        <v>457.78</v>
+      </c>
+      <c r="D393" t="n">
+        <v>463.82</v>
+      </c>
+      <c r="E393" t="n">
+        <v>467.08</v>
+      </c>
+      <c r="F393" t="n">
+        <v>467.98</v>
+      </c>
+      <c r="G393" t="n">
+        <v>464.49</v>
+      </c>
+      <c r="H393" t="n">
+        <v>484.04</v>
+      </c>
+      <c r="I393" t="n">
+        <v>494.54</v>
+      </c>
+      <c r="J393" t="n">
+        <v>502.79</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>468.63</v>
+      </c>
+      <c r="C394" t="n">
+        <v>458.89</v>
+      </c>
+      <c r="D394" t="n">
+        <v>464.65</v>
+      </c>
+      <c r="E394" t="n">
+        <v>466.21</v>
+      </c>
+      <c r="F394" t="n">
+        <v>467.09</v>
+      </c>
+      <c r="G394" t="n">
+        <v>465.01</v>
+      </c>
+      <c r="H394" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="I394" t="n">
+        <v>495.06</v>
+      </c>
+      <c r="J394" t="n">
+        <v>502.44</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19751,6 +19829,26 @@
       </c>
       <c r="B400" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -19919,28 +20017,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.303405271337102</v>
+        <v>6.300799667995731</v>
       </c>
       <c r="J2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5459085812064759</v>
+        <v>0.5486413194919402</v>
       </c>
       <c r="M2" t="n">
-        <v>32.7634090876084</v>
+        <v>32.61519363010306</v>
       </c>
       <c r="N2" t="n">
-        <v>1894.22090926298</v>
+        <v>1884.61944903684</v>
       </c>
       <c r="O2" t="n">
-        <v>43.52264823356892</v>
+        <v>43.41220391821682</v>
       </c>
       <c r="P2" t="n">
-        <v>301.9945057088601</v>
+        <v>302.0208514027983</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19997,28 +20095,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.208300005159076</v>
+        <v>6.201587221997293</v>
       </c>
       <c r="J3" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K3" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6555667489460679</v>
+        <v>0.657714027567518</v>
       </c>
       <c r="M3" t="n">
-        <v>28.4976304000773</v>
+        <v>28.39842768276228</v>
       </c>
       <c r="N3" t="n">
-        <v>1160.620761858459</v>
+        <v>1154.932885823523</v>
       </c>
       <c r="O3" t="n">
-        <v>34.06788461085394</v>
+        <v>33.98430352123643</v>
       </c>
       <c r="P3" t="n">
-        <v>299.4436890261941</v>
+        <v>299.5115849019363</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20075,28 +20173,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.289849979937255</v>
+        <v>6.284194344684646</v>
       </c>
       <c r="J4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6564909945286503</v>
+        <v>0.6587305218216595</v>
       </c>
       <c r="M4" t="n">
-        <v>28.90303534749686</v>
+        <v>28.79539100754134</v>
       </c>
       <c r="N4" t="n">
-        <v>1186.442566540307</v>
+        <v>1180.559595374089</v>
       </c>
       <c r="O4" t="n">
-        <v>34.44477560589279</v>
+        <v>34.35927233475833</v>
       </c>
       <c r="P4" t="n">
-        <v>302.1335065665571</v>
+        <v>302.190710761636</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20153,28 +20251,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.503289971686864</v>
+        <v>6.499367544181664</v>
       </c>
       <c r="J5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6627222063962803</v>
+        <v>0.6650892756516569</v>
       </c>
       <c r="M5" t="n">
-        <v>29.631879455718</v>
+        <v>29.51018163352148</v>
       </c>
       <c r="N5" t="n">
-        <v>1233.613900105356</v>
+        <v>1227.411937364905</v>
       </c>
       <c r="O5" t="n">
-        <v>35.12284014861777</v>
+        <v>35.03443930427466</v>
       </c>
       <c r="P5" t="n">
-        <v>297.1494619491867</v>
+        <v>297.1891429824399</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20231,28 +20329,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.298417758714357</v>
+        <v>6.295895438450151</v>
       </c>
       <c r="J6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6795375368600685</v>
+        <v>0.6819380500094643</v>
       </c>
       <c r="M6" t="n">
-        <v>27.52373564744371</v>
+        <v>27.40226741832567</v>
       </c>
       <c r="N6" t="n">
-        <v>1072.218835169557</v>
+        <v>1066.794691161078</v>
       </c>
       <c r="O6" t="n">
-        <v>32.74475278834087</v>
+        <v>32.66182314508909</v>
       </c>
       <c r="P6" t="n">
-        <v>302.1212102289929</v>
+        <v>302.146729203334</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20309,28 +20407,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.315406408079648</v>
+        <v>6.310787027651046</v>
       </c>
       <c r="J7" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K7" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6728338824577458</v>
+        <v>0.6751015717908767</v>
       </c>
       <c r="M7" t="n">
-        <v>27.77744769437847</v>
+        <v>27.66973221952741</v>
       </c>
       <c r="N7" t="n">
-        <v>1111.526612109311</v>
+        <v>1105.973135794633</v>
       </c>
       <c r="O7" t="n">
-        <v>33.3395652657516</v>
+        <v>33.25617440107375</v>
       </c>
       <c r="P7" t="n">
-        <v>300.9490481099218</v>
+        <v>300.9957720495279</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20387,28 +20485,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.134848373223862</v>
+        <v>7.132320392186049</v>
       </c>
       <c r="J8" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K8" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6758306775892575</v>
+        <v>0.6782674993896727</v>
       </c>
       <c r="M8" t="n">
-        <v>31.81747071973056</v>
+        <v>31.674497320526</v>
       </c>
       <c r="N8" t="n">
-        <v>1399.459385867433</v>
+        <v>1392.36998752827</v>
       </c>
       <c r="O8" t="n">
-        <v>37.4093489099641</v>
+        <v>37.31447423625676</v>
       </c>
       <c r="P8" t="n">
-        <v>295.9156304677806</v>
+        <v>295.9412066251865</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20465,28 +20563,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.679830306943333</v>
+        <v>7.676309828911848</v>
       </c>
       <c r="J9" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K9" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.678598314265618</v>
+        <v>0.680975812833598</v>
       </c>
       <c r="M9" t="n">
-        <v>34.17677574041283</v>
+        <v>34.02895387170267</v>
       </c>
       <c r="N9" t="n">
-        <v>1601.015045173995</v>
+        <v>1592.92729201872</v>
       </c>
       <c r="O9" t="n">
-        <v>40.01268605297569</v>
+        <v>39.91149323213452</v>
       </c>
       <c r="P9" t="n">
-        <v>293.5484653793059</v>
+        <v>293.5840742131251</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20543,28 +20641,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.711888387211888</v>
+        <v>7.711513216987387</v>
       </c>
       <c r="J10" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K10" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6834894759513621</v>
+        <v>0.6860320613068873</v>
       </c>
       <c r="M10" t="n">
-        <v>33.88301227265173</v>
+        <v>33.71335203064467</v>
       </c>
       <c r="N10" t="n">
-        <v>1578.463650926519</v>
+        <v>1570.43202182916</v>
       </c>
       <c r="O10" t="n">
-        <v>39.72988360071697</v>
+        <v>39.6286767610169</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4162213316531</v>
+        <v>297.4200194680628</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20602,7 +20700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K392"/>
+  <dimension ref="A1:K394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42949,6 +43047,120 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-42.217884403895816,173.8644019113616</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-42.21795870948663,173.86350259911416</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-42.218125944272494,173.8627967823237</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-42.2183862360046,173.86217993215905</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-42.21866848084106,173.8614818484319</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-42.21898417652902,173.86077714885562</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-42.21949526580672,173.8601798479505</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-42.219904679830854,173.8596089208893</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-42.220348702107806,173.85908237993291</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-42.21790499747018,173.86440847440477</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-42.217968436682,173.8635056990147</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-42.21813297502347,173.86280019655018</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-42.218379282758335,173.86217507417808</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-42.21866164614606,173.86147621589814</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-42.218988036711735,173.86078071570833</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-42.21948907097597,173.8601740068591</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-42.21990833538455,173.85961285870246</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-42.220346353428894,173.85907955185084</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K394"/>
+  <dimension ref="A1:K396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15810,6 +15810,84 @@
         <v>502.44</v>
       </c>
       <c r="K394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>470.66</v>
+      </c>
+      <c r="C395" t="n">
+        <v>458.82</v>
+      </c>
+      <c r="D395" t="n">
+        <v>465.25</v>
+      </c>
+      <c r="E395" t="n">
+        <v>464.75</v>
+      </c>
+      <c r="F395" t="n">
+        <v>465.39</v>
+      </c>
+      <c r="G395" t="n">
+        <v>463.99</v>
+      </c>
+      <c r="H395" t="n">
+        <v>482.54</v>
+      </c>
+      <c r="I395" t="n">
+        <v>494.88</v>
+      </c>
+      <c r="J395" t="n">
+        <v>502.81</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>471.15</v>
+      </c>
+      <c r="C396" t="n">
+        <v>461.1</v>
+      </c>
+      <c r="D396" t="n">
+        <v>467.11</v>
+      </c>
+      <c r="E396" t="n">
+        <v>466.27</v>
+      </c>
+      <c r="F396" t="n">
+        <v>466.36</v>
+      </c>
+      <c r="G396" t="n">
+        <v>464.07</v>
+      </c>
+      <c r="H396" t="n">
+        <v>482.92</v>
+      </c>
+      <c r="I396" t="n">
+        <v>495.39</v>
+      </c>
+      <c r="J396" t="n">
+        <v>503.34</v>
+      </c>
+      <c r="K396" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15826,7 +15904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19849,6 +19927,26 @@
       </c>
       <c r="B402" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -20017,28 +20115,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.300799667995731</v>
+        <v>6.301113702599757</v>
       </c>
       <c r="J2" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5486413194919402</v>
+        <v>0.5515905549530664</v>
       </c>
       <c r="M2" t="n">
-        <v>32.61519363010306</v>
+        <v>32.45094894852117</v>
       </c>
       <c r="N2" t="n">
-        <v>1884.61944903684</v>
+        <v>1875.077707089059</v>
       </c>
       <c r="O2" t="n">
-        <v>43.41220391821682</v>
+        <v>43.30216746410113</v>
       </c>
       <c r="P2" t="n">
-        <v>302.0208514027983</v>
+        <v>302.0176608057839</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20095,28 +20193,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.201587221997293</v>
+        <v>6.19606785950345</v>
       </c>
       <c r="J3" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K3" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L3" t="n">
-        <v>0.657714027567518</v>
+        <v>0.6599397220905761</v>
       </c>
       <c r="M3" t="n">
-        <v>28.39842768276228</v>
+        <v>28.29183999271727</v>
       </c>
       <c r="N3" t="n">
-        <v>1154.932885823523</v>
+        <v>1149.239841922393</v>
       </c>
       <c r="O3" t="n">
-        <v>33.98430352123643</v>
+        <v>33.90044014349066</v>
       </c>
       <c r="P3" t="n">
-        <v>299.5115849019363</v>
+        <v>299.5676419434087</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20173,28 +20271,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.284194344684646</v>
+        <v>6.280015272328055</v>
       </c>
       <c r="J4" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6587305218216595</v>
+        <v>0.6610670869278017</v>
       </c>
       <c r="M4" t="n">
-        <v>28.79539100754134</v>
+        <v>28.67837381963278</v>
       </c>
       <c r="N4" t="n">
-        <v>1180.559595374089</v>
+        <v>1174.671185784155</v>
       </c>
       <c r="O4" t="n">
-        <v>34.35927233475833</v>
+        <v>34.27347641813061</v>
       </c>
       <c r="P4" t="n">
-        <v>302.190710761636</v>
+        <v>302.2331550044298</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20251,28 +20349,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.499367544181664</v>
+        <v>6.493753997253506</v>
       </c>
       <c r="J5" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K5" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6650892756516569</v>
+        <v>0.667304405656945</v>
       </c>
       <c r="M5" t="n">
-        <v>29.51018163352148</v>
+        <v>29.40190797784296</v>
       </c>
       <c r="N5" t="n">
-        <v>1227.411937364905</v>
+        <v>1221.353634167526</v>
       </c>
       <c r="O5" t="n">
-        <v>35.03443930427466</v>
+        <v>34.94787023793476</v>
       </c>
       <c r="P5" t="n">
-        <v>297.1891429824399</v>
+        <v>297.2461585076842</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20329,28 +20427,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.295895438450151</v>
+        <v>6.291134334683924</v>
       </c>
       <c r="J6" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K6" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6819380500094643</v>
+        <v>0.6841461099859062</v>
       </c>
       <c r="M6" t="n">
-        <v>27.40226741832567</v>
+        <v>27.29821044382608</v>
       </c>
       <c r="N6" t="n">
-        <v>1066.794691161078</v>
+        <v>1061.504873579902</v>
       </c>
       <c r="O6" t="n">
-        <v>32.66182314508909</v>
+        <v>32.58074390771184</v>
       </c>
       <c r="P6" t="n">
-        <v>302.146729203334</v>
+        <v>302.195087462736</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20407,28 +20505,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.310787027651046</v>
+        <v>6.304929086513487</v>
       </c>
       <c r="J7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6751015717908767</v>
+        <v>0.677249064419694</v>
       </c>
       <c r="M7" t="n">
-        <v>27.66973221952741</v>
+        <v>27.57176696804103</v>
       </c>
       <c r="N7" t="n">
-        <v>1105.973135794633</v>
+        <v>1100.54097200095</v>
       </c>
       <c r="O7" t="n">
-        <v>33.25617440107375</v>
+        <v>33.1744023608708</v>
       </c>
       <c r="P7" t="n">
-        <v>300.9957720495279</v>
+        <v>301.0552734040574</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20485,28 +20583,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.132320392186049</v>
+        <v>7.128248394890101</v>
       </c>
       <c r="J8" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K8" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6782674993896727</v>
+        <v>0.6805798734071836</v>
       </c>
       <c r="M8" t="n">
-        <v>31.674497320526</v>
+        <v>31.54428124117214</v>
       </c>
       <c r="N8" t="n">
-        <v>1392.36998752827</v>
+        <v>1385.401114047765</v>
       </c>
       <c r="O8" t="n">
-        <v>37.31447423625676</v>
+        <v>37.22097680136518</v>
       </c>
       <c r="P8" t="n">
-        <v>295.9412066251865</v>
+        <v>295.982566830352</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20563,28 +20661,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.676309828911848</v>
+        <v>7.672455121985952</v>
       </c>
       <c r="J9" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K9" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L9" t="n">
-        <v>0.680975812833598</v>
+        <v>0.6833103221710957</v>
       </c>
       <c r="M9" t="n">
-        <v>34.02895387170267</v>
+        <v>33.88489052557547</v>
       </c>
       <c r="N9" t="n">
-        <v>1592.92729201872</v>
+        <v>1584.934603720217</v>
       </c>
       <c r="O9" t="n">
-        <v>39.91149323213452</v>
+        <v>39.81123715385164</v>
       </c>
       <c r="P9" t="n">
-        <v>293.5840742131251</v>
+        <v>293.6232270523707</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20641,28 +20739,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.711513216987387</v>
+        <v>7.710846360307272</v>
       </c>
       <c r="J10" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K10" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6860320613068873</v>
+        <v>0.6885344024091871</v>
       </c>
       <c r="M10" t="n">
-        <v>33.71335203064467</v>
+        <v>33.54752737090416</v>
       </c>
       <c r="N10" t="n">
-        <v>1570.43202182916</v>
+        <v>1562.482803865931</v>
       </c>
       <c r="O10" t="n">
-        <v>39.6286767610169</v>
+        <v>39.52825323570384</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4200194680628</v>
+        <v>297.4267921154771</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20700,7 +20798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K394"/>
+  <dimension ref="A1:K396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43161,6 +43259,120 @@
         </is>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-42.21792278681274,173.86441414376043</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-42.21796782325525,173.86350550352543</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-42.21813805749399,173.86280266466622</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-42.21836761409169,173.86216692170674</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-42.21864859110984,173.86146545712927</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-42.21898046481474,173.86077371918995</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-42.21948420360873,173.86016941743094</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-42.21990707000059,173.85961149561322</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-42.220348836318024,173.85908254153765</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-42.217927080791924,173.8644155122261</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-42.217987803439996,173.86351187089159</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-42.218153813152185,173.86281031582843</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-42.218379762292564,173.86217540921123</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-42.21865604016006,173.86147159595566</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-42.21898105868904,173.86077426793642</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-42.21948700603232,173.86017205982887</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-42.219910655255106,173.8596153576995</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-42.2203523928888,173.85908682406233</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K396"/>
+  <dimension ref="A1:K399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15888,6 +15888,123 @@
         <v>503.34</v>
       </c>
       <c r="K396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>469.79</v>
+      </c>
+      <c r="C397" t="n">
+        <v>459.7</v>
+      </c>
+      <c r="D397" t="n">
+        <v>465.67</v>
+      </c>
+      <c r="E397" t="n">
+        <v>465.75</v>
+      </c>
+      <c r="F397" t="n">
+        <v>465.24</v>
+      </c>
+      <c r="G397" t="n">
+        <v>463.51</v>
+      </c>
+      <c r="H397" t="n">
+        <v>482.7</v>
+      </c>
+      <c r="I397" t="n">
+        <v>495.62</v>
+      </c>
+      <c r="J397" t="n">
+        <v>502.74</v>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>474.95</v>
+      </c>
+      <c r="C398" t="n">
+        <v>464.42</v>
+      </c>
+      <c r="D398" t="n">
+        <v>468.85</v>
+      </c>
+      <c r="E398" t="n">
+        <v>466.7</v>
+      </c>
+      <c r="F398" t="n">
+        <v>466.85</v>
+      </c>
+      <c r="G398" t="n">
+        <v>464.48</v>
+      </c>
+      <c r="H398" t="n">
+        <v>482.78</v>
+      </c>
+      <c r="I398" t="n">
+        <v>495.96</v>
+      </c>
+      <c r="J398" t="n">
+        <v>502.19</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>474.06</v>
+      </c>
+      <c r="C399" t="n">
+        <v>463.42</v>
+      </c>
+      <c r="D399" t="n">
+        <v>467.94</v>
+      </c>
+      <c r="E399" t="n">
+        <v>466.51</v>
+      </c>
+      <c r="F399" t="n">
+        <v>467.06</v>
+      </c>
+      <c r="G399" t="n">
+        <v>464.51</v>
+      </c>
+      <c r="H399" t="n">
+        <v>483.13</v>
+      </c>
+      <c r="I399" t="n">
+        <v>496</v>
+      </c>
+      <c r="J399" t="n">
+        <v>502.15</v>
+      </c>
+      <c r="K399" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15904,7 +16021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B404"/>
+  <dimension ref="A1:B407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19947,6 +20064,36 @@
       </c>
       <c r="B404" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -20115,28 +20262,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.301113702599757</v>
+        <v>6.304002179069669</v>
       </c>
       <c r="J2" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K2" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5515905549530664</v>
+        <v>0.5561167841806826</v>
       </c>
       <c r="M2" t="n">
-        <v>32.45094894852117</v>
+        <v>32.21982110343122</v>
       </c>
       <c r="N2" t="n">
-        <v>1875.077707089059</v>
+        <v>1861.006476831415</v>
       </c>
       <c r="O2" t="n">
-        <v>43.30216746410113</v>
+        <v>43.13938428896981</v>
       </c>
       <c r="P2" t="n">
-        <v>302.0176608057839</v>
+        <v>301.9882215903236</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20193,28 +20340,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.19606785950345</v>
+        <v>6.191306224227298</v>
       </c>
       <c r="J3" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K3" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6599397220905761</v>
+        <v>0.6634778285770807</v>
       </c>
       <c r="M3" t="n">
-        <v>28.29183999271727</v>
+        <v>28.11030047941932</v>
       </c>
       <c r="N3" t="n">
-        <v>1149.239841922393</v>
+        <v>1140.681221803716</v>
       </c>
       <c r="O3" t="n">
-        <v>33.90044014349066</v>
+        <v>33.77397254993431</v>
       </c>
       <c r="P3" t="n">
-        <v>299.5676419434087</v>
+        <v>299.6161158966829</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20271,28 +20418,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.280015272328055</v>
+        <v>6.275337824261952</v>
       </c>
       <c r="J4" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K4" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6610670869278017</v>
+        <v>0.6646140902894788</v>
       </c>
       <c r="M4" t="n">
-        <v>28.67837381963278</v>
+        <v>28.49402951592469</v>
       </c>
       <c r="N4" t="n">
-        <v>1174.671185784155</v>
+        <v>1165.901722380239</v>
       </c>
       <c r="O4" t="n">
-        <v>34.27347641813061</v>
+        <v>34.14530307934371</v>
       </c>
       <c r="P4" t="n">
-        <v>302.2331550044298</v>
+        <v>302.2807807655951</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20349,28 +20496,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.493753997253506</v>
+        <v>6.486239441340377</v>
       </c>
       <c r="J5" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K5" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L5" t="n">
-        <v>0.667304405656945</v>
+        <v>0.6706179115401536</v>
       </c>
       <c r="M5" t="n">
-        <v>29.40190797784296</v>
+        <v>29.23468859014765</v>
       </c>
       <c r="N5" t="n">
-        <v>1221.353634167526</v>
+        <v>1212.336659684632</v>
       </c>
       <c r="O5" t="n">
-        <v>34.94787023793476</v>
+        <v>34.81862518372361</v>
       </c>
       <c r="P5" t="n">
-        <v>297.2461585076842</v>
+        <v>297.3226861636836</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20427,28 +20574,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.291134334683924</v>
+        <v>6.284428881535433</v>
       </c>
       <c r="J6" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K6" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6841461099859062</v>
+        <v>0.6874119841151987</v>
       </c>
       <c r="M6" t="n">
-        <v>27.29821044382608</v>
+        <v>27.14070795813238</v>
       </c>
       <c r="N6" t="n">
-        <v>1061.504873579902</v>
+        <v>1053.657131030501</v>
       </c>
       <c r="O6" t="n">
-        <v>32.58074390771184</v>
+        <v>32.46008519752376</v>
       </c>
       <c r="P6" t="n">
-        <v>302.195087462736</v>
+        <v>302.2633676191567</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20505,28 +20652,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.304929086513487</v>
+        <v>6.296081976504911</v>
       </c>
       <c r="J7" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K7" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L7" t="n">
-        <v>0.677249064419694</v>
+        <v>0.6803855984756559</v>
       </c>
       <c r="M7" t="n">
-        <v>27.57176696804103</v>
+        <v>27.4268021472557</v>
       </c>
       <c r="N7" t="n">
-        <v>1100.54097200095</v>
+        <v>1092.507507270069</v>
       </c>
       <c r="O7" t="n">
-        <v>33.1744023608708</v>
+        <v>33.0531013260491</v>
       </c>
       <c r="P7" t="n">
-        <v>301.0552734040574</v>
+        <v>301.1453699217055</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20583,28 +20730,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.128248394890101</v>
+        <v>7.121912503605418</v>
       </c>
       <c r="J8" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K8" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6805798734071836</v>
+        <v>0.6839526422685097</v>
       </c>
       <c r="M8" t="n">
-        <v>31.54428124117214</v>
+        <v>31.35287384162269</v>
       </c>
       <c r="N8" t="n">
-        <v>1385.401114047765</v>
+        <v>1375.09231278894</v>
       </c>
       <c r="O8" t="n">
-        <v>37.22097680136518</v>
+        <v>37.08223715997917</v>
       </c>
       <c r="P8" t="n">
-        <v>295.982566830352</v>
+        <v>296.047092348207</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20661,28 +20808,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.672455121985952</v>
+        <v>7.667239015945102</v>
       </c>
       <c r="J9" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K9" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6833103221710957</v>
+        <v>0.6867660551305588</v>
       </c>
       <c r="M9" t="n">
-        <v>33.88489052557547</v>
+        <v>33.66721992199533</v>
       </c>
       <c r="N9" t="n">
-        <v>1584.934603720217</v>
+        <v>1573.078724493138</v>
       </c>
       <c r="O9" t="n">
-        <v>39.81123715385164</v>
+        <v>39.66205648340916</v>
       </c>
       <c r="P9" t="n">
-        <v>293.6232270523707</v>
+        <v>293.6763496753871</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20739,28 +20886,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.710846360307272</v>
+        <v>7.708105699809586</v>
       </c>
       <c r="J10" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K10" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6885344024091871</v>
+        <v>0.6921058393363786</v>
       </c>
       <c r="M10" t="n">
-        <v>33.54752737090416</v>
+        <v>33.31461033724718</v>
       </c>
       <c r="N10" t="n">
-        <v>1562.482803865931</v>
+        <v>1550.731883638909</v>
       </c>
       <c r="O10" t="n">
-        <v>39.52825323570384</v>
+        <v>39.37933320459996</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4267921154771</v>
+        <v>297.4547108566248</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20798,7 +20945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K396"/>
+  <dimension ref="A1:K399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43373,6 +43520,177 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-42.21791516280883,173.86441171403615</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-42.21797553490556,173.8635079611049</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-42.21814161522331,173.86280439234767</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-42.21837560632918,173.8621725055909</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-42.21864743919484,173.86146450782633</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-42.218976901568944,173.86077042671127</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-42.21948538357656,173.86017053001953</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-42.21991227213455,173.85961709942484</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-42.22034836658225,173.85908197592119</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-42.21796038103795,173.86442612482332</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-42.21801689739236,173.86352114267774</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-42.21816855231578,173.86281747337077</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-42.21838319895454,173.8621778102822</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-42.21865980308219,173.86147469701285</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-42.218984102294726,173.8607770802623</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-42.21948597356049,173.86017108631384</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-42.219914662304106,173.85961967414937</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-42.22034467580105,173.85907753179234</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-42.217952581769914,173.86442363924033</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-42.21800813415379,173.86351834997015</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-42.21816084390271,173.86281373005798</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-42.21838168042948,173.86217674934383</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>-42.21866141576307,173.86147602603748</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-42.21898432499757,173.86077728604226</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-42.21948855474006,173.8601735201015</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-42.219914943500534,173.85961997705817</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-42.2203444073806,173.85907720858302</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0386/nzd0386.xlsx
+++ b/data/nzd0386/nzd0386.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K399"/>
+  <dimension ref="A1:K400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16005,6 +16005,45 @@
         <v>502.15</v>
       </c>
       <c r="K399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>473.74</v>
+      </c>
+      <c r="C400" t="n">
+        <v>462.89</v>
+      </c>
+      <c r="D400" t="n">
+        <v>467.9</v>
+      </c>
+      <c r="E400" t="n">
+        <v>466.32</v>
+      </c>
+      <c r="F400" t="n">
+        <v>466.95</v>
+      </c>
+      <c r="G400" t="n">
+        <v>464.36</v>
+      </c>
+      <c r="H400" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="I400" t="n">
+        <v>496.03</v>
+      </c>
+      <c r="J400" t="n">
+        <v>501.98</v>
+      </c>
+      <c r="K400" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16021,7 +16060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B407"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20094,6 +20133,16 @@
       </c>
       <c r="B407" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -20262,28 +20311,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>6.304002179069669</v>
+        <v>6.305085159129247</v>
       </c>
       <c r="J2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5561167841806826</v>
+        <v>0.5576228893516393</v>
       </c>
       <c r="M2" t="n">
-        <v>32.21982110343122</v>
+        <v>32.14217335275065</v>
       </c>
       <c r="N2" t="n">
-        <v>1861.006476831415</v>
+        <v>1856.354237906035</v>
       </c>
       <c r="O2" t="n">
-        <v>43.13938428896981</v>
+        <v>43.08542953140928</v>
       </c>
       <c r="P2" t="n">
-        <v>301.9882215903236</v>
+        <v>301.977154456066</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20340,28 +20389,28 @@
         <v>0.0595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.191306224227298</v>
+        <v>6.189698200297308</v>
       </c>
       <c r="J3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6634778285770807</v>
+        <v>0.6646431334176501</v>
       </c>
       <c r="M3" t="n">
-        <v>28.11030047941932</v>
+        <v>28.05045607619385</v>
       </c>
       <c r="N3" t="n">
-        <v>1140.681221803716</v>
+        <v>1137.848690361496</v>
       </c>
       <c r="O3" t="n">
-        <v>33.77397254993431</v>
+        <v>33.73201284183165</v>
       </c>
       <c r="P3" t="n">
-        <v>299.6161158966829</v>
+        <v>299.632548532321</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20418,28 +20467,28 @@
         <v>0.073</v>
       </c>
       <c r="I4" t="n">
-        <v>6.275337824261952</v>
+        <v>6.273773122705843</v>
       </c>
       <c r="J4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6646140902894788</v>
+        <v>0.6657824428411043</v>
       </c>
       <c r="M4" t="n">
-        <v>28.49402951592469</v>
+        <v>28.43316372730702</v>
       </c>
       <c r="N4" t="n">
-        <v>1165.901722380239</v>
+        <v>1163.004582640614</v>
       </c>
       <c r="O4" t="n">
-        <v>34.14530307934371</v>
+        <v>34.10285299854858</v>
       </c>
       <c r="P4" t="n">
-        <v>302.2807807655951</v>
+        <v>302.2967706834531</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20496,28 +20545,28 @@
         <v>0.1158</v>
       </c>
       <c r="I5" t="n">
-        <v>6.486239441340377</v>
+        <v>6.483539037216149</v>
       </c>
       <c r="J5" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6706179115401536</v>
+        <v>0.6716932012764285</v>
       </c>
       <c r="M5" t="n">
-        <v>29.23468859014765</v>
+        <v>29.18079866637747</v>
       </c>
       <c r="N5" t="n">
-        <v>1212.336659684632</v>
+        <v>1209.372444780874</v>
       </c>
       <c r="O5" t="n">
-        <v>34.81862518372361</v>
+        <v>34.77603261990755</v>
       </c>
       <c r="P5" t="n">
-        <v>297.3226861636836</v>
+        <v>297.3502819949534</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20574,28 +20623,28 @@
         <v>0.0964</v>
       </c>
       <c r="I6" t="n">
-        <v>6.284428881535433</v>
+        <v>6.282284960299885</v>
       </c>
       <c r="J6" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K6" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6874119841151987</v>
+        <v>0.6884937957787984</v>
       </c>
       <c r="M6" t="n">
-        <v>27.14070795813238</v>
+        <v>27.08797802333262</v>
       </c>
       <c r="N6" t="n">
-        <v>1053.657131030501</v>
+        <v>1051.063170378101</v>
       </c>
       <c r="O6" t="n">
-        <v>32.46008519752376</v>
+        <v>32.42010441652064</v>
       </c>
       <c r="P6" t="n">
-        <v>302.2633676191567</v>
+        <v>302.2852766690432</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20652,28 +20701,28 @@
         <v>0.1215</v>
       </c>
       <c r="I7" t="n">
-        <v>6.296081976504911</v>
+        <v>6.29305265979939</v>
       </c>
       <c r="J7" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K7" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6803855984756559</v>
+        <v>0.6814107126401265</v>
       </c>
       <c r="M7" t="n">
-        <v>27.4268021472557</v>
+        <v>27.37941208387504</v>
       </c>
       <c r="N7" t="n">
-        <v>1092.507507270069</v>
+        <v>1089.862798061131</v>
       </c>
       <c r="O7" t="n">
-        <v>33.0531013260491</v>
+        <v>33.01307010959646</v>
       </c>
       <c r="P7" t="n">
-        <v>301.1453699217055</v>
+        <v>301.1763269595497</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20730,28 +20779,28 @@
         <v>0.0993</v>
       </c>
       <c r="I8" t="n">
-        <v>7.121912503605418</v>
+        <v>7.119499093377191</v>
       </c>
       <c r="J8" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K8" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6839526422685097</v>
+        <v>0.6850422022694783</v>
       </c>
       <c r="M8" t="n">
-        <v>31.35287384162269</v>
+        <v>31.29180626590397</v>
       </c>
       <c r="N8" t="n">
-        <v>1375.09231278894</v>
+        <v>1371.705250801159</v>
       </c>
       <c r="O8" t="n">
-        <v>37.08223715997917</v>
+        <v>37.036539400991</v>
       </c>
       <c r="P8" t="n">
-        <v>296.047092348207</v>
+        <v>296.0717553461802</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20808,28 +20857,28 @@
         <v>0.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>7.667239015945102</v>
+        <v>7.665324695366641</v>
       </c>
       <c r="J9" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K9" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6867660551305588</v>
+        <v>0.6878928312442201</v>
       </c>
       <c r="M9" t="n">
-        <v>33.66721992199533</v>
+        <v>33.59657552336561</v>
       </c>
       <c r="N9" t="n">
-        <v>1573.078724493138</v>
+        <v>1569.173471345775</v>
       </c>
       <c r="O9" t="n">
-        <v>39.66205648340916</v>
+        <v>39.6127942885348</v>
       </c>
       <c r="P9" t="n">
-        <v>293.6763496753871</v>
+        <v>293.6959124020194</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20886,28 +20935,28 @@
         <v>0.0835</v>
       </c>
       <c r="I10" t="n">
-        <v>7.708105699809586</v>
+        <v>7.70672135796045</v>
       </c>
       <c r="J10" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K10" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6921058393363786</v>
+        <v>0.6932541734139964</v>
       </c>
       <c r="M10" t="n">
-        <v>33.31461033724718</v>
+        <v>33.24114964592368</v>
       </c>
       <c r="N10" t="n">
-        <v>1550.731883638909</v>
+        <v>1546.864843498044</v>
       </c>
       <c r="O10" t="n">
-        <v>39.37933320459996</v>
+        <v>39.33020268824004</v>
       </c>
       <c r="P10" t="n">
-        <v>297.4547108566248</v>
+        <v>297.4688576518195</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20945,7 +20994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K399"/>
+  <dimension ref="A1:K400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43691,6 +43740,63 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-42.21794977753869,173.86442274554773</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-42.21800348963732,173.86351686983545</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-42.21816050507135,173.86281356551677</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-42.21838016190443,173.8621756884055</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-42.218660571025474,173.86147532988173</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-42.218983211483305,173.8607762571425</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-42.219485531072536,173.8601706690931</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-42.219915154397825,173.85962020423975</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-42.22034326659365,173.8590758349433</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
